--- a/salidas/empresas/LYB.xlsx
+++ b/salidas/empresas/LYB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B2" t="n">
-        <v>8.809248924255371</v>
+        <v>8.809252738952637</v>
       </c>
       <c r="C2" t="n">
         <v>22.29999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B3" t="n">
-        <v>7.019750118255615</v>
+        <v>7.019752025604248</v>
       </c>
       <c r="C3" t="n">
         <v>17.77000045776367</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B4" t="n">
-        <v>6.379796028137207</v>
+        <v>6.379795074462891</v>
       </c>
       <c r="C4" t="n">
         <v>16.14999961853027</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B5" t="n">
-        <v>7.11060905456543</v>
+        <v>7.110608100891113</v>
       </c>
       <c r="C5" t="n">
         <v>18</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B6" t="n">
-        <v>8.098193168640137</v>
+        <v>8.09819221496582</v>
       </c>
       <c r="C6" t="n">
         <v>20.5</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B7" t="n">
-        <v>9.441308975219727</v>
+        <v>9.441303253173828</v>
       </c>
       <c r="C7" t="n">
         <v>23.89999961853027</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B8" t="n">
-        <v>10.61060619354248</v>
+        <v>10.61060428619385</v>
       </c>
       <c r="C8" t="n">
         <v>26.86000061035156</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53893947601318</v>
+        <v>11.53893852233887</v>
       </c>
       <c r="C9" t="n">
         <v>29.20999908447266</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B11" t="n">
-        <v>14.19751262664795</v>
+        <v>14.19751453399658</v>
       </c>
       <c r="C11" t="n">
         <v>35.93999862670898</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B12" t="n">
-        <v>15.04288482666016</v>
+        <v>15.04288768768311</v>
       </c>
       <c r="C12" t="n">
         <v>38.08000183105469</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B13" t="n">
-        <v>15.6235818862915</v>
+        <v>15.62357997894287</v>
       </c>
       <c r="C13" t="n">
         <v>39.54999923706055</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B15" t="n">
-        <v>17.34444999694824</v>
+        <v>17.34444808959961</v>
       </c>
       <c r="C15" t="n">
         <v>43.81000137329102</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B16" t="n">
-        <v>15.2501335144043</v>
+        <v>15.25013256072998</v>
       </c>
       <c r="C16" t="n">
         <v>38.52000045776367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B17" t="n">
-        <v>15.62227344512939</v>
+        <v>15.62228107452393</v>
       </c>
       <c r="C17" t="n">
         <v>39.45999908447266</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B18" t="n">
-        <v>13.79940509796143</v>
+        <v>13.79940223693848</v>
       </c>
       <c r="C18" t="n">
         <v>34.65000152587891</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B19" t="n">
-        <v>9.729280471801758</v>
+        <v>9.729277610778809</v>
       </c>
       <c r="C19" t="n">
         <v>24.43000030517578</v>
@@ -830,7 +842,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B20" t="n">
@@ -855,11 +867,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B21" t="n">
-        <v>15.08753108978271</v>
+        <v>15.08752727508545</v>
       </c>
       <c r="C21" t="n">
         <v>32.66999816894531</v>
@@ -880,11 +892,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B22" t="n">
-        <v>15.00440216064453</v>
+        <v>15.00440502166748</v>
       </c>
       <c r="C22" t="n">
         <v>32.4900016784668</v>
@@ -905,11 +917,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B23" t="n">
-        <v>19.90427589416504</v>
+        <v>19.90427207946777</v>
       </c>
       <c r="C23" t="n">
         <v>43.09999847412109</v>
@@ -930,7 +942,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B24" t="n">
@@ -955,11 +967,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B25" t="n">
-        <v>20.28317070007324</v>
+        <v>20.28316688537598</v>
       </c>
       <c r="C25" t="n">
         <v>43.65000152587891</v>
@@ -980,11 +992,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B26" t="n">
-        <v>19.41421699523926</v>
+        <v>19.41422653198242</v>
       </c>
       <c r="C26" t="n">
         <v>41.77999877929688</v>
@@ -1005,11 +1017,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B27" t="n">
-        <v>18.52511024475098</v>
+        <v>18.52510261535645</v>
       </c>
       <c r="C27" t="n">
         <v>39.45999908447266</v>
@@ -1030,11 +1042,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B28" t="n">
-        <v>18.90537261962891</v>
+        <v>18.90537643432617</v>
       </c>
       <c r="C28" t="n">
         <v>40.27000045776367</v>
@@ -1055,11 +1067,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B29" t="n">
-        <v>20.90530014038086</v>
+        <v>20.9052906036377</v>
       </c>
       <c r="C29" t="n">
         <v>44.52999877929688</v>
@@ -1080,11 +1092,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B30" t="n">
-        <v>23.12428283691406</v>
+        <v>23.1242847442627</v>
       </c>
       <c r="C30" t="n">
         <v>48.84000015258789</v>
@@ -1105,11 +1117,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B31" t="n">
-        <v>24.45948219299316</v>
+        <v>24.4594898223877</v>
       </c>
       <c r="C31" t="n">
         <v>51.65999984741211</v>
@@ -1130,11 +1142,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B32" t="n">
-        <v>25.27857971191406</v>
+        <v>25.27858352661133</v>
       </c>
       <c r="C32" t="n">
         <v>53.38999938964844</v>
@@ -1155,11 +1167,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B33" t="n">
-        <v>25.15594863891602</v>
+        <v>25.15594291687012</v>
       </c>
       <c r="C33" t="n">
         <v>49.72999954223633</v>
@@ -1180,11 +1192,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B34" t="n">
-        <v>28.87899971008301</v>
+        <v>28.87900352478027</v>
       </c>
       <c r="C34" t="n">
         <v>57.09000015258789</v>
@@ -1205,11 +1217,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B35" t="n">
-        <v>32.08103942871094</v>
+        <v>32.08103179931641</v>
       </c>
       <c r="C35" t="n">
         <v>63.41999816894531</v>
@@ -1230,11 +1242,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B36" t="n">
-        <v>29.85110664367676</v>
+        <v>29.85110092163086</v>
       </c>
       <c r="C36" t="n">
         <v>58.61999893188477</v>
@@ -1259,7 +1271,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B37" t="n">
@@ -1288,11 +1300,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B38" t="n">
-        <v>30.91030120849609</v>
+        <v>30.91031265258789</v>
       </c>
       <c r="C38" t="n">
         <v>60.70000076293945</v>
@@ -1317,11 +1329,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B39" t="n">
-        <v>34.19821166992188</v>
+        <v>34.19821548461914</v>
       </c>
       <c r="C39" t="n">
         <v>66.65000152587891</v>
@@ -1346,7 +1358,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B40" t="n">
@@ -1375,11 +1387,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B41" t="n">
-        <v>35.25519180297852</v>
+        <v>35.25519943237305</v>
       </c>
       <c r="C41" t="n">
         <v>68.70999908447266</v>
@@ -1404,11 +1416,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B42" t="n">
-        <v>35.99406814575195</v>
+        <v>35.99407958984375</v>
       </c>
       <c r="C42" t="n">
         <v>70.15000152587891</v>
@@ -1433,11 +1445,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B43" t="n">
-        <v>37.83222961425781</v>
+        <v>37.83224487304688</v>
       </c>
       <c r="C43" t="n">
         <v>73.23000335693359</v>
@@ -1462,11 +1474,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B44" t="n">
-        <v>38.54001617431641</v>
+        <v>38.53999710083008</v>
       </c>
       <c r="C44" t="n">
         <v>74.59999847412109</v>
@@ -1491,11 +1503,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B45" t="n">
-        <v>40.18395614624023</v>
+        <v>40.18395233154297</v>
       </c>
       <c r="C45" t="n">
         <v>77.18000030517578</v>
@@ -1520,7 +1532,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B46" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B47" t="n">
-        <v>41.00658416748047</v>
+        <v>41.00659942626953</v>
       </c>
       <c r="C47" t="n">
         <v>78.76000213623047</v>
@@ -1578,11 +1590,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B48" t="n">
-        <v>46.17599105834961</v>
+        <v>46.17599868774414</v>
       </c>
       <c r="C48" t="n">
         <v>88.08000183105469</v>
@@ -1607,7 +1619,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B49" t="n">
@@ -1636,11 +1648,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B50" t="n">
-        <v>48.86376571655273</v>
+        <v>48.86376953125</v>
       </c>
       <c r="C50" t="n">
         <v>92.5</v>
@@ -1665,11 +1677,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B51" t="n">
-        <v>52.59854507446289</v>
+        <v>52.59853744506836</v>
       </c>
       <c r="C51" t="n">
         <v>99.56999969482422</v>
@@ -1694,11 +1706,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B52" t="n">
-        <v>51.58428573608398</v>
+        <v>51.58426666259766</v>
       </c>
       <c r="C52" t="n">
         <v>97.65000152587891</v>
@@ -1723,11 +1735,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B53" t="n">
-        <v>56.12729644775391</v>
+        <v>56.12730407714844</v>
       </c>
       <c r="C53" t="n">
         <v>106.25</v>
@@ -1752,11 +1764,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B54" t="n">
-        <v>60.78551483154297</v>
+        <v>60.78549957275391</v>
       </c>
       <c r="C54" t="n">
         <v>114.3499984741211</v>
@@ -1781,7 +1793,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B55" t="n">
@@ -1810,11 +1822,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B56" t="n">
-        <v>48.70814895629883</v>
+        <v>48.7081298828125</v>
       </c>
       <c r="C56" t="n">
         <v>91.62999725341797</v>
@@ -1839,11 +1851,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B57" t="n">
-        <v>42.25095367431641</v>
+        <v>42.25094985961914</v>
       </c>
       <c r="C57" t="n">
         <v>78.86000061035156</v>
@@ -1868,11 +1880,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B58" t="n">
-        <v>42.5349235534668</v>
+        <v>42.53490829467773</v>
       </c>
       <c r="C58" t="n">
         <v>79.38999938964844</v>
@@ -1897,7 +1909,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B59" t="n">
@@ -1926,7 +1938,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B60" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B61" t="n">
@@ -1984,11 +1996,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B62" t="n">
-        <v>55.89983749389648</v>
+        <v>55.89984893798828</v>
       </c>
       <c r="C62" t="n">
         <v>103.5199966430664</v>
@@ -2013,11 +2025,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B63" t="n">
-        <v>54.59306335449219</v>
+        <v>54.59304809570312</v>
       </c>
       <c r="C63" t="n">
         <v>101.0999984741211</v>
@@ -2042,11 +2054,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B64" t="n">
-        <v>55.89983749389648</v>
+        <v>55.89984893798828</v>
       </c>
       <c r="C64" t="n">
         <v>103.5199966430664</v>
@@ -2071,11 +2083,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B65" t="n">
-        <v>50.66733932495117</v>
+        <v>50.66733551025391</v>
       </c>
       <c r="C65" t="n">
         <v>93.83000183105469</v>
@@ -2100,11 +2112,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B66" t="n">
-        <v>46.5369987487793</v>
+        <v>46.53701782226562</v>
       </c>
       <c r="C66" t="n">
         <v>85.37999725341797</v>
@@ -2129,11 +2141,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B67" t="n">
-        <v>45.43600082397461</v>
+        <v>45.43598937988281</v>
       </c>
       <c r="C67" t="n">
         <v>83.36000061035156</v>
@@ -2158,11 +2170,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B68" t="n">
-        <v>50.64130401611328</v>
+        <v>50.64129638671875</v>
       </c>
       <c r="C68" t="n">
         <v>92.91000366210938</v>
@@ -2187,11 +2199,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B69" t="n">
-        <v>52.65945816040039</v>
+        <v>52.65944671630859</v>
       </c>
       <c r="C69" t="n">
         <v>95.81999969482422</v>
@@ -2216,11 +2228,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B70" t="n">
-        <v>47.75732421875</v>
+        <v>47.75732040405273</v>
       </c>
       <c r="C70" t="n">
         <v>86.90000152587891</v>
@@ -2245,7 +2257,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B71" t="n">
@@ -2274,11 +2286,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B72" t="n">
-        <v>44.52453994750977</v>
+        <v>44.52452850341797</v>
       </c>
       <c r="C72" t="n">
         <v>80.20999908447266</v>
@@ -2303,11 +2315,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B73" t="n">
-        <v>47.50540924072266</v>
+        <v>47.50541687011719</v>
       </c>
       <c r="C73" t="n">
         <v>85.58000183105469</v>
@@ -2332,11 +2344,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B74" t="n">
-        <v>45.89008331298828</v>
+        <v>45.89009857177734</v>
       </c>
       <c r="C74" t="n">
         <v>82.66999816894531</v>
@@ -2361,11 +2373,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B75" t="n">
-        <v>45.64288330078125</v>
+        <v>45.64287948608398</v>
       </c>
       <c r="C75" t="n">
         <v>81.36000061035156</v>
@@ -2390,11 +2402,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B76" t="n">
-        <v>41.74953460693359</v>
+        <v>41.74955749511719</v>
       </c>
       <c r="C76" t="n">
         <v>74.41999816894531</v>
@@ -2419,11 +2431,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B77" t="n">
-        <v>42.22077941894531</v>
+        <v>42.22078704833984</v>
       </c>
       <c r="C77" t="n">
         <v>75.26000213623047</v>
@@ -2448,11 +2460,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B78" t="n">
-        <v>44.75363540649414</v>
+        <v>44.75362396240234</v>
       </c>
       <c r="C78" t="n">
         <v>78.88999938964844</v>
@@ -2477,11 +2489,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B79" t="n">
-        <v>45.75775146484375</v>
+        <v>45.75773239135742</v>
       </c>
       <c r="C79" t="n">
         <v>80.66000366210938</v>
@@ -2506,11 +2518,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B80" t="n">
-        <v>45.12804412841797</v>
+        <v>45.12804794311523</v>
       </c>
       <c r="C80" t="n">
         <v>79.55000305175781</v>
@@ -2535,11 +2547,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B81" t="n">
-        <v>51.74541854858398</v>
+        <v>51.74543762207031</v>
       </c>
       <c r="C81" t="n">
         <v>90.31999969482422</v>
@@ -2564,11 +2576,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B82" t="n">
-        <v>49.1444091796875</v>
+        <v>49.1443977355957</v>
       </c>
       <c r="C82" t="n">
         <v>85.77999877929688</v>
@@ -2593,11 +2605,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B83" t="n">
-        <v>53.43551254272461</v>
+        <v>53.43552398681641</v>
       </c>
       <c r="C83" t="n">
         <v>93.26999664306641</v>
@@ -2622,11 +2634,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B84" t="n">
-        <v>52.27250671386719</v>
+        <v>52.27249145507812</v>
       </c>
       <c r="C84" t="n">
         <v>91.23999786376953</v>
@@ -2651,7 +2663,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B85" t="n">
@@ -2680,11 +2692,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B86" t="n">
-        <v>49.00366592407227</v>
+        <v>49.00368499755859</v>
       </c>
       <c r="C86" t="n">
         <v>84.76000213623047</v>
@@ -2709,11 +2721,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B87" t="n">
-        <v>46.55233764648438</v>
+        <v>46.55233001708984</v>
       </c>
       <c r="C87" t="n">
         <v>80.51999664306641</v>
@@ -2738,11 +2750,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B88" t="n">
-        <v>49.34126663208008</v>
+        <v>49.34128189086914</v>
       </c>
       <c r="C88" t="n">
         <v>84.38999938964844</v>
@@ -2767,7 +2779,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B89" t="n">
@@ -2796,11 +2808,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B90" t="n">
-        <v>52.9662971496582</v>
+        <v>52.96628952026367</v>
       </c>
       <c r="C90" t="n">
         <v>90.58999633789062</v>
@@ -2825,7 +2837,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B91" t="n">
@@ -2854,11 +2866,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B92" t="n">
-        <v>61.13948059082031</v>
+        <v>61.13949203491211</v>
       </c>
       <c r="C92" t="n">
         <v>103.5299987792969</v>
@@ -2883,11 +2895,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B93" t="n">
-        <v>61.83043670654297</v>
+        <v>61.83041763305664</v>
       </c>
       <c r="C93" t="n">
         <v>104.6999969482422</v>
@@ -2912,11 +2924,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B94" t="n">
-        <v>65.71746826171875</v>
+        <v>65.71746063232422</v>
       </c>
       <c r="C94" t="n">
         <v>110.3199996948242</v>
@@ -2941,11 +2953,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B95" t="n">
-        <v>71.38853454589844</v>
+        <v>71.38850402832031</v>
       </c>
       <c r="C95" t="n">
         <v>119.8399963378906</v>
@@ -2970,11 +2982,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B96" t="n">
-        <v>64.46649169921875</v>
+        <v>64.46651458740234</v>
       </c>
       <c r="C96" t="n">
         <v>108.2200012207031</v>
@@ -2999,11 +3011,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B97" t="n">
-        <v>63.54108428955078</v>
+        <v>63.54105758666992</v>
       </c>
       <c r="C97" t="n">
         <v>105.6800003051758</v>
@@ -3028,11 +3040,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B98" t="n">
-        <v>63.57113265991211</v>
+        <v>63.57112884521484</v>
       </c>
       <c r="C98" t="n">
         <v>105.7300033569336</v>
@@ -3057,11 +3069,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B99" t="n">
-        <v>67.41316223144531</v>
+        <v>67.41316986083984</v>
       </c>
       <c r="C99" t="n">
         <v>112.120002746582</v>
@@ -3086,11 +3098,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B100" t="n">
-        <v>66.6102294921875</v>
+        <v>66.61024475097656</v>
       </c>
       <c r="C100" t="n">
         <v>109.8499984741211</v>
@@ -3115,11 +3127,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B101" t="n">
-        <v>67.18023681640625</v>
+        <v>67.18022918701172</v>
       </c>
       <c r="C101" t="n">
         <v>110.7900009155273</v>
@@ -3144,7 +3156,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B102" t="n">
@@ -3173,11 +3185,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B103" t="n">
-        <v>62.71551895141602</v>
+        <v>62.71554946899414</v>
       </c>
       <c r="C103" t="n">
         <v>102.5100021362305</v>
@@ -3202,11 +3214,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B104" t="n">
-        <v>54.61530303955078</v>
+        <v>54.61531448364258</v>
       </c>
       <c r="C104" t="n">
         <v>89.26999664306641</v>
@@ -3231,11 +3243,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B105" t="n">
-        <v>57.08699417114258</v>
+        <v>57.08698654174805</v>
       </c>
       <c r="C105" t="n">
         <v>93.30999755859375</v>
@@ -3260,11 +3272,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B106" t="n">
-        <v>51.46046447753906</v>
+        <v>51.46047973632812</v>
       </c>
       <c r="C106" t="n">
         <v>83.16000366210938</v>
@@ -3289,11 +3301,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B107" t="n">
-        <v>53.81815719604492</v>
+        <v>53.81815338134766</v>
       </c>
       <c r="C107" t="n">
         <v>86.97000122070312</v>
@@ -3318,11 +3330,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B108" t="n">
-        <v>52.92087554931641</v>
+        <v>52.92086410522461</v>
       </c>
       <c r="C108" t="n">
         <v>85.51999664306641</v>
@@ -3347,11 +3359,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B109" t="n">
-        <v>52.64538955688477</v>
+        <v>52.64538192749023</v>
       </c>
       <c r="C109" t="n">
         <v>84.08000183105469</v>
@@ -3376,11 +3388,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B110" t="n">
-        <v>55.24385833740234</v>
+        <v>55.24382781982422</v>
       </c>
       <c r="C110" t="n">
         <v>88.23000335693359</v>
@@ -3405,11 +3417,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B111" t="n">
-        <v>46.490478515625</v>
+        <v>46.49047470092773</v>
       </c>
       <c r="C111" t="n">
         <v>74.25</v>
@@ -3434,11 +3446,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B112" t="n">
-        <v>54.64292907714844</v>
+        <v>54.64292526245117</v>
       </c>
       <c r="C112" t="n">
         <v>86.12999725341797</v>
@@ -3463,11 +3475,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B113" t="n">
-        <v>53.09493255615234</v>
+        <v>53.09493637084961</v>
       </c>
       <c r="C113" t="n">
         <v>83.69000244140625</v>
@@ -3492,11 +3504,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B114" t="n">
-        <v>49.09169769287109</v>
+        <v>49.09171295166016</v>
       </c>
       <c r="C114" t="n">
         <v>77.37999725341797</v>
@@ -3521,11 +3533,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B115" t="n">
-        <v>57.542724609375</v>
+        <v>57.54271697998047</v>
       </c>
       <c r="C115" t="n">
         <v>89.47000122070312</v>
@@ -3550,11 +3562,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B116" t="n">
-        <v>57.69063949584961</v>
+        <v>57.69064712524414</v>
       </c>
       <c r="C116" t="n">
         <v>89.69999694824219</v>
@@ -3579,11 +3591,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B117" t="n">
-        <v>60.18558120727539</v>
+        <v>60.18558502197266</v>
       </c>
       <c r="C117" t="n">
         <v>92.54000091552734</v>
@@ -3608,11 +3620,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B118" t="n">
-        <v>61.44729232788086</v>
+        <v>61.44728469848633</v>
       </c>
       <c r="C118" t="n">
         <v>94.48000335693359</v>
@@ -3637,11 +3649,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B119" t="n">
-        <v>50.63808441162109</v>
+        <v>50.63809204101562</v>
       </c>
       <c r="C119" t="n">
         <v>77.86000061035156</v>
@@ -3666,7 +3678,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B120" t="n">
@@ -3695,11 +3707,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B121" t="n">
-        <v>32.76324462890625</v>
+        <v>32.76325988769531</v>
       </c>
       <c r="C121" t="n">
         <v>49.63000106811523</v>
@@ -3724,11 +3736,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B122" t="n">
-        <v>38.25569915771484</v>
+        <v>38.25569534301758</v>
       </c>
       <c r="C122" t="n">
         <v>57.95000076293945</v>
@@ -3753,7 +3765,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B123" t="n">
@@ -3782,7 +3794,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B124" t="n">
@@ -3811,7 +3823,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B125" t="n">
@@ -3840,11 +3852,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B126" t="n">
-        <v>44.52762222290039</v>
+        <v>44.52761459350586</v>
       </c>
       <c r="C126" t="n">
         <v>65.48000335693359</v>
@@ -3869,11 +3881,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B127" t="n">
-        <v>47.93451690673828</v>
+        <v>47.93450546264648</v>
       </c>
       <c r="C127" t="n">
         <v>70.48999786376953</v>
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B128" t="n">
@@ -3927,11 +3939,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B129" t="n">
-        <v>58.55787658691406</v>
+        <v>58.5578727722168</v>
       </c>
       <c r="C129" t="n">
         <v>85.09999847412109</v>
@@ -3956,11 +3968,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B130" t="n">
-        <v>63.07185363769531</v>
+        <v>63.07186126708984</v>
       </c>
       <c r="C130" t="n">
         <v>91.66000366210938</v>
@@ -3985,11 +3997,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B131" t="n">
-        <v>59.01203155517578</v>
+        <v>59.01203918457031</v>
       </c>
       <c r="C131" t="n">
         <v>85.76000213623047</v>
@@ -4014,7 +4026,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B132" t="n">
@@ -4043,11 +4055,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B133" t="n">
-        <v>72.31266784667969</v>
+        <v>72.31266021728516</v>
       </c>
       <c r="C133" t="n">
         <v>104.0500030517578</v>
@@ -4072,7 +4084,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B134" t="n">
@@ -4101,11 +4113,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B135" t="n">
-        <v>78.26862335205078</v>
+        <v>78.26863861083984</v>
       </c>
       <c r="C135" t="n">
         <v>112.620002746582</v>
@@ -4130,7 +4142,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B136" t="n">
@@ -4159,11 +4171,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B137" t="n">
-        <v>69.70062255859375</v>
+        <v>69.70063018798828</v>
       </c>
       <c r="C137" t="n">
         <v>99.33000183105469</v>
@@ -4188,11 +4200,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B138" t="n">
-        <v>71.21159362792969</v>
+        <v>71.21158599853516</v>
       </c>
       <c r="C138" t="n">
         <v>100.3499984741211</v>
@@ -4217,11 +4229,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B139" t="n">
-        <v>66.59899139404297</v>
+        <v>66.59897613525391</v>
       </c>
       <c r="C139" t="n">
         <v>93.84999847412109</v>
@@ -4246,11 +4258,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B140" t="n">
-        <v>65.86806488037109</v>
+        <v>65.86805725097656</v>
       </c>
       <c r="C140" t="n">
         <v>92.81999969482422</v>
@@ -4275,11 +4287,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B141" t="n">
-        <v>62.60287475585938</v>
+        <v>62.60286331176758</v>
       </c>
       <c r="C141" t="n">
         <v>87.12999725341797</v>
@@ -4304,11 +4316,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B142" t="n">
-        <v>66.26721954345703</v>
+        <v>66.2672119140625</v>
       </c>
       <c r="C142" t="n">
         <v>92.23000335693359</v>
@@ -4333,11 +4345,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B143" t="n">
-        <v>69.50046539306641</v>
+        <v>69.50047302246094</v>
       </c>
       <c r="C143" t="n">
         <v>96.73000335693359</v>
@@ -4362,11 +4374,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B144" t="n">
-        <v>69.85973358154297</v>
+        <v>69.85971832275391</v>
       </c>
       <c r="C144" t="n">
         <v>97.23000335693359</v>
@@ -4391,11 +4403,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B145" t="n">
-        <v>74.72200775146484</v>
+        <v>74.72201538085938</v>
       </c>
       <c r="C145" t="n">
         <v>102.8199996948242</v>
@@ -4420,7 +4432,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B146" t="n">
@@ -4449,7 +4461,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B147" t="n">
@@ -4478,7 +4490,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B148" t="n">
@@ -4507,7 +4519,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B149" t="n">
@@ -4536,7 +4548,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B150" t="n">
@@ -4565,11 +4577,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B151" t="n">
-        <v>58.68910980224609</v>
+        <v>58.68912124633789</v>
       </c>
       <c r="C151" t="n">
         <v>75.27999877929688</v>
@@ -4594,11 +4606,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>59.60126876831055</v>
+        <v>59.60126113891602</v>
       </c>
       <c r="C152" t="n">
         <v>76.44999694824219</v>
@@ -4623,11 +4635,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B153" t="n">
-        <v>67.18229675292969</v>
+        <v>67.18231201171875</v>
       </c>
       <c r="C153" t="n">
         <v>85.01000213623047</v>
@@ -4652,11 +4664,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B154" t="n">
-        <v>65.6175537109375</v>
+        <v>65.61753082275391</v>
       </c>
       <c r="C154" t="n">
         <v>83.02999877929688</v>
@@ -4681,11 +4693,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B155" t="n">
-        <v>76.41286468505859</v>
+        <v>76.41285705566406</v>
       </c>
       <c r="C155" t="n">
         <v>96.69000244140625</v>
@@ -4710,7 +4722,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B156" t="n">
@@ -4739,11 +4751,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B157" t="n">
-        <v>75.11505889892578</v>
+        <v>75.11504364013672</v>
       </c>
       <c r="C157" t="n">
         <v>93.88999938964844</v>
@@ -4768,7 +4780,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B158" t="n">
@@ -4797,11 +4809,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B159" t="n">
-        <v>69.41220092773438</v>
+        <v>69.41220855712891</v>
       </c>
       <c r="C159" t="n">
         <v>85.54000091552734</v>
@@ -4826,11 +4838,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B160" t="n">
-        <v>74.51627349853516</v>
+        <v>74.51628875732422</v>
       </c>
       <c r="C160" t="n">
         <v>91.83000183105469</v>
@@ -4855,7 +4867,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B161" t="n">
@@ -4884,11 +4896,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B162" t="n">
-        <v>81.19107055664062</v>
+        <v>81.19106292724609</v>
       </c>
       <c r="C162" t="n">
         <v>98.76999664306641</v>
@@ -4913,11 +4925,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B163" t="n">
-        <v>77.84544372558594</v>
+        <v>77.84543609619141</v>
       </c>
       <c r="C163" t="n">
         <v>94.69999694824219</v>
@@ -4942,11 +4954,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B164" t="n">
-        <v>74.17922973632812</v>
+        <v>74.17922210693359</v>
       </c>
       <c r="C164" t="n">
         <v>90.23999786376953</v>
@@ -4971,11 +4983,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B165" t="n">
-        <v>79.21702575683594</v>
+        <v>79.21700286865234</v>
       </c>
       <c r="C165" t="n">
         <v>95.09999847412109</v>
@@ -5000,7 +5012,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B166" t="n">
@@ -5029,11 +5041,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B167" t="n">
-        <v>78.40070343017578</v>
+        <v>78.40069580078125</v>
       </c>
       <c r="C167" t="n">
         <v>94.12000274658203</v>
@@ -5058,11 +5070,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B168" t="n">
-        <v>83.53188323974609</v>
+        <v>83.53187561035156</v>
       </c>
       <c r="C168" t="n">
         <v>100.2799987792969</v>
@@ -5087,11 +5099,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B169" t="n">
-        <v>86.27327728271484</v>
+        <v>86.27326965332031</v>
       </c>
       <c r="C169" t="n">
         <v>102.2799987792969</v>
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B170" t="n">
@@ -5145,11 +5157,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B171" t="n">
-        <v>83.86085510253906</v>
+        <v>83.86084747314453</v>
       </c>
       <c r="C171" t="n">
         <v>99.41999816894531</v>
@@ -5174,7 +5186,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B172" t="n">
@@ -5203,7 +5215,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B173" t="n">
@@ -5232,11 +5244,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B174" t="n">
-        <v>85.55738067626953</v>
+        <v>85.55738830566406</v>
       </c>
       <c r="C174" t="n">
         <v>98.69999694824219</v>
@@ -5261,11 +5273,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B175" t="n">
-        <v>83.13023376464844</v>
+        <v>83.13022613525391</v>
       </c>
       <c r="C175" t="n">
         <v>95.90000152587891</v>
@@ -5290,11 +5302,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B176" t="n">
-        <v>75.28528594970703</v>
+        <v>75.28529357910156</v>
       </c>
       <c r="C176" t="n">
         <v>86.84999847412109</v>
@@ -5319,7 +5331,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B177" t="n">
@@ -5348,11 +5360,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B178" t="n">
-        <v>65.43247985839844</v>
+        <v>65.4324951171875</v>
       </c>
       <c r="C178" t="n">
         <v>74.26999664306641</v>
@@ -5377,7 +5389,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B179" t="n">
@@ -5406,7 +5418,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B180" t="n">
@@ -5435,11 +5447,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B181" t="n">
-        <v>63.11425018310547</v>
+        <v>63.11425399780273</v>
       </c>
       <c r="C181" t="n">
         <v>70.40000152587891</v>
@@ -5464,11 +5476,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B182" t="n">
-        <v>52.18579483032227</v>
+        <v>52.18579864501953</v>
       </c>
       <c r="C182" t="n">
         <v>58.20999908447266</v>
@@ -5493,7 +5505,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B183" t="n">
@@ -5522,7 +5534,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B184" t="n">
@@ -5551,7 +5563,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B185" t="n">
@@ -5580,11 +5592,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B186" t="n">
-        <v>53.0096321105957</v>
+        <v>53.00963592529297</v>
       </c>
       <c r="C186" t="n">
         <v>56.34999847412109</v>
@@ -5609,11 +5621,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B187" t="n">
-        <v>46.13296508789062</v>
+        <v>46.13296890258789</v>
       </c>
       <c r="C187" t="n">
         <v>49.04000091552734</v>
@@ -5638,7 +5650,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B188" t="n">
@@ -5665,7 +5677,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B189" t="n">
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B190" t="n">
@@ -5719,7 +5731,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B191" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B192" t="n">
@@ -5773,7 +5785,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B193" t="n">
@@ -5800,7 +5812,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B194" t="n">
@@ -5827,7 +5839,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B195" t="n">
@@ -5854,7 +5866,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B196" t="n">
@@ -5881,7 +5893,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B197" t="n">
@@ -5908,7 +5920,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B198" t="n">
@@ -5935,17 +5947,17 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B199" t="n">
-        <v>59.97000122070312</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="C199" t="n">
-        <v>59.97000122070312</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="D199" t="n">
-        <v>59378100</v>
+        <v>61959000</v>
       </c>
       <c r="E199" t="n">
         <v>-1.130000000000002</v>
@@ -5955,10 +5967,10 @@
         <v>323037952</v>
       </c>
       <c r="H199" t="n">
-        <v>19372586375.77344</v>
+        <v>19440424049.94336</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1838115293648221</v>
+        <v>0.191800993091982</v>
       </c>
     </row>
   </sheetData>
@@ -5990,75 +6002,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6094,13 +6106,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6136,13 +6148,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6178,13 +6190,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6211,7 +6223,7 @@
       <c r="I5" t="n">
         <v>3.66</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K5" t="n">
@@ -6224,13 +6236,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6257,7 +6269,7 @@
       <c r="I6" t="n">
         <v>3.55</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K6" t="n">
@@ -6270,13 +6282,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6303,7 +6315,7 @@
       <c r="I7" t="n">
         <v>3.5</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K7" t="n">
@@ -6316,13 +6328,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6349,7 +6361,7 @@
       <c r="I8" t="n">
         <v>3.45</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K8" t="n">
@@ -6362,13 +6374,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6395,7 +6407,7 @@
       <c r="I9" t="n">
         <v>4.92</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K9" t="n">
@@ -6408,13 +6420,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6441,7 +6453,7 @@
       <c r="I10" t="n">
         <v>5.43</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K10" t="n">
@@ -6454,13 +6466,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6487,7 +6499,7 @@
       <c r="I11" t="n">
         <v>5.71</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K11" t="n">
@@ -6500,13 +6512,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6533,7 +6545,7 @@
       <c r="I12" t="n">
         <v>5.75</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="K12" t="n">
@@ -6546,13 +6558,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6579,7 +6591,7 @@
       <c r="I13" t="n">
         <v>6.77</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K13" t="n">
@@ -6592,13 +6604,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6625,7 +6637,7 @@
       <c r="I14" t="n">
         <v>6.94</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K14" t="n">
@@ -6638,13 +6650,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6671,7 +6683,7 @@
       <c r="I15" t="n">
         <v>7.56</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K15" t="n">
@@ -6684,13 +6696,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6717,7 +6729,7 @@
       <c r="I16" t="n">
         <v>8.51</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K16" t="n">
@@ -6730,13 +6742,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6763,7 +6775,7 @@
       <c r="I17" t="n">
         <v>7.94</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="K17" t="n">
@@ -6776,13 +6788,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6809,7 +6821,7 @@
       <c r="I18" t="n">
         <v>8.629999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="K18" t="n">
@@ -6822,13 +6834,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6855,7 +6867,7 @@
       <c r="I19" t="n">
         <v>9.219999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="K19" t="n">
@@ -6868,13 +6880,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6901,7 +6913,7 @@
       <c r="I20" t="n">
         <v>9.309999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K20" t="n">
@@ -6914,13 +6926,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6947,7 +6959,7 @@
       <c r="I21" t="n">
         <v>9.549999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K21" t="n">
@@ -6960,13 +6972,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6993,7 +7005,7 @@
       <c r="I22" t="n">
         <v>9.509999999999998</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="K22" t="n">
@@ -7006,13 +7018,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7039,7 +7051,7 @@
       <c r="I23" t="n">
         <v>9.249999999999998</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K23" t="n">
@@ -7052,13 +7064,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7085,7 +7097,7 @@
       <c r="I24" t="n">
         <v>9.01</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K24" t="n">
@@ -7098,13 +7110,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7131,7 +7143,7 @@
       <c r="I25" t="n">
         <v>9.1</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K25" t="n">
@@ -7144,13 +7156,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7177,7 +7189,7 @@
       <c r="I26" t="n">
         <v>8.709999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K26" t="n">
@@ -7190,13 +7202,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7223,7 +7235,7 @@
       <c r="I27" t="n">
         <v>8.959999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K27" t="n">
@@ -7236,13 +7248,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7269,7 +7281,7 @@
       <c r="I28" t="n">
         <v>9.33</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K28" t="n">
@@ -7282,13 +7294,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7315,7 +7327,7 @@
       <c r="I29" t="n">
         <v>12.25</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K29" t="n">
@@ -7328,13 +7340,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7361,7 +7373,7 @@
       <c r="I30" t="n">
         <v>13.38</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K30" t="n">
@@ -7374,13 +7386,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7407,7 +7419,7 @@
       <c r="I31" t="n">
         <v>14.79</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K31" t="n">
@@ -7420,13 +7432,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7453,7 +7465,7 @@
       <c r="I32" t="n">
         <v>14.97</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K32" t="n">
@@ -7466,13 +7478,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7499,7 +7511,7 @@
       <c r="I33" t="n">
         <v>12.01</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K33" t="n">
@@ -7512,13 +7524,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7545,7 +7557,7 @@
       <c r="I34" t="n">
         <v>11.09</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K34" t="n">
@@ -7558,13 +7570,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7591,7 +7603,7 @@
       <c r="I35" t="n">
         <v>9.569999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K35" t="n">
@@ -7604,13 +7616,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7637,7 +7649,7 @@
       <c r="I36" t="n">
         <v>9.569999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K36" t="n">
@@ -7650,13 +7662,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7683,7 +7695,7 @@
       <c r="I37" t="n">
         <v>9.569999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K37" t="n">
@@ -7696,13 +7708,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7729,7 +7741,7 @@
       <c r="I38" t="n">
         <v>7.799999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K38" t="n">
@@ -7742,13 +7754,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7775,7 +7787,7 @@
       <c r="I39" t="n">
         <v>6.039999999999998</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K39" t="n">
@@ -7788,13 +7800,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7821,7 +7833,7 @@
       <c r="I40" t="n">
         <v>3.519999999999998</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K40" t="n">
@@ -7834,13 +7846,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7867,7 +7879,7 @@
       <c r="I41" t="n">
         <v>4.239999999999998</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K41" t="n">
@@ -7880,13 +7892,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7913,7 +7925,7 @@
       <c r="I42" t="n">
         <v>6.999999999999998</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K42" t="n">
@@ -7926,13 +7938,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7959,7 +7971,7 @@
       <c r="I43" t="n">
         <v>12.19</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K43" t="n">
@@ -7972,13 +7984,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8005,7 +8017,7 @@
       <c r="I44" t="n">
         <v>17.11</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K44" t="n">
@@ -8018,13 +8030,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8051,7 +8063,7 @@
       <c r="I45" t="n">
         <v>16.75</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K45" t="n">
@@ -8064,13 +8076,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8097,7 +8109,7 @@
       <c r="I46" t="n">
         <v>17.57</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K46" t="n">
@@ -8110,13 +8122,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8143,7 +8155,7 @@
       <c r="I47" t="n">
         <v>16.42</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K47" t="n">
@@ -8156,13 +8168,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8189,7 +8201,7 @@
       <c r="I48" t="n">
         <v>12.92</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K48" t="n">
@@ -8202,13 +8214,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8235,7 +8247,7 @@
       <c r="I49" t="n">
         <v>11.81</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K49" t="n">
@@ -8248,13 +8260,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8281,7 +8293,7 @@
       <c r="I50" t="n">
         <v>9.249999999999998</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K50" t="n">
@@ -8294,13 +8306,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8327,7 +8339,7 @@
       <c r="I51" t="n">
         <v>6.449999999999998</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K51" t="n">
@@ -8340,13 +8352,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8373,7 +8385,7 @@
       <c r="I52" t="n">
         <v>6.989999999999998</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K52" t="n">
@@ -8386,13 +8398,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8419,7 +8431,7 @@
       <c r="I53" t="n">
         <v>6.459999999999998</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K53" t="n">
@@ -8432,13 +8444,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8465,7 +8477,7 @@
       <c r="I54" t="n">
         <v>6.459999999999997</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K54" t="n">
@@ -8478,13 +8490,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8511,7 +8523,7 @@
       <c r="I55" t="n">
         <v>7.099999999999998</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K55" t="n">
@@ -8524,13 +8536,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8557,7 +8569,7 @@
       <c r="I56" t="n">
         <v>6.559999999999998</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K56" t="n">
@@ -8570,13 +8582,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8603,7 +8615,7 @@
       <c r="I57" t="n">
         <v>4.149999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K57" t="n">
@@ -8616,13 +8628,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8649,7 +8661,7 @@
       <c r="I58" t="n">
         <v>3.249999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K58" t="n">
@@ -8662,13 +8674,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8695,7 +8707,7 @@
       <c r="I59" t="n">
         <v>0.7699999999999989</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K59" t="n">
@@ -8708,13 +8720,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8741,7 +8753,7 @@
       <c r="I60" t="n">
         <v>-3.750000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K60" t="n">
@@ -8754,13 +8766,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -8787,7 +8799,7 @@
       <c r="I61" t="n">
         <v>-2.340000000000002</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K61" t="n">
@@ -8800,13 +8812,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -8833,7 +8845,7 @@
       <c r="I62" t="n">
         <v>-2.500000000000002</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K62" t="n">
@@ -8846,13 +8858,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -8879,7 +8891,7 @@
       <c r="I63" t="n">
         <v>-1.130000000000002</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K63" t="n">
@@ -8916,52 +8928,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40798</v>
       </c>
       <c r="C2" t="n">
@@ -8990,10 +9002,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C3" t="n">
@@ -9022,10 +9034,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40963</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C4" t="n">
@@ -9054,10 +9066,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="C5" t="n">
@@ -9086,10 +9098,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41114</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C6" t="n">
@@ -9118,10 +9130,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41206</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C7" t="n">
@@ -9150,10 +9162,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="C8" t="n">
@@ -9182,10 +9194,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41388</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C9" t="n">
@@ -9214,10 +9226,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41479</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C10" t="n">
@@ -9246,10 +9258,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41572</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C11" t="n">
@@ -9278,10 +9290,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41688</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C12" t="n">
@@ -9310,10 +9322,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C13" t="n">
@@ -9342,10 +9354,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41843</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C14" t="n">
@@ -9374,10 +9386,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41934</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C15" t="n">
@@ -9406,10 +9418,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="C16" t="n">
@@ -9438,10 +9450,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42116</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="C17" t="n">
@@ -9470,10 +9482,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42208</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="C18" t="n">
@@ -9502,10 +9514,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42297</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C19" t="n">
@@ -9534,10 +9546,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42411</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="C20" t="n">
@@ -9566,10 +9578,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="C21" t="n">
@@ -9598,10 +9610,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42577</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C22" t="n">
@@ -9630,10 +9642,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42670</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C23" t="n">
@@ -9662,10 +9674,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42780</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C24" t="n">
@@ -9694,10 +9706,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42850</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C25" t="n">
@@ -9726,10 +9738,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42941</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C26" t="n">
@@ -9758,10 +9770,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43032</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C27" t="n">
@@ -9790,10 +9802,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43151</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C28" t="n">
@@ -9822,10 +9834,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43214</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C29" t="n">
@@ -9854,10 +9866,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C30" t="n">
@@ -9886,10 +9898,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C31" t="n">
@@ -9918,10 +9930,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43515</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C32" t="n">
@@ -9950,10 +9962,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C33" t="n">
@@ -9982,10 +9994,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C34" t="n">
@@ -10014,10 +10026,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43768</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C35" t="n">
@@ -10046,10 +10058,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43879</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C36" t="n">
@@ -10078,10 +10090,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43950</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C37" t="n">
@@ -10110,10 +10122,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C38" t="n">
@@ -10142,10 +10154,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44132</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C39" t="n">
@@ -10174,10 +10186,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44250</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C40" t="n">
@@ -10206,10 +10218,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44314</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C41" t="n">
@@ -10238,10 +10250,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C42" t="n">
@@ -10270,10 +10282,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44496</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C43" t="n">
@@ -10302,10 +10314,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44614</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C44" t="n">
@@ -10334,10 +10346,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C45" t="n">
@@ -10366,10 +10378,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C46" t="n">
@@ -10398,10 +10410,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44860</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C47" t="n">
@@ -10430,10 +10442,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44978</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C48" t="n">
@@ -10462,10 +10474,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C49" t="n">
@@ -10494,10 +10506,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45140</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C50" t="n">
@@ -10526,10 +10538,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C51" t="n">
@@ -10558,10 +10570,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45342</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C52" t="n">
@@ -10590,10 +10602,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C53" t="n">
@@ -10622,10 +10634,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C54" t="n">
@@ -10654,10 +10666,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C55" t="n">
@@ -10686,10 +10698,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45713</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C56" t="n">
@@ -10718,10 +10730,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C57" t="n">
@@ -10750,10 +10762,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C58" t="n">
@@ -10782,10 +10794,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45959</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C59" t="n">
@@ -10814,10 +10826,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46071</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C60" t="n">
@@ -10846,10 +10858,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C61" t="n">
@@ -10878,10 +10890,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46232</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C62" t="n">
@@ -10928,12 +10940,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/LYB.xlsx
+++ b/salidas/empresas/LYB.xlsx
@@ -498,7 +498,7 @@
         <v>40298</v>
       </c>
       <c r="B2" t="n">
-        <v>8.809252738952637</v>
+        <v>8.809256553649902</v>
       </c>
       <c r="C2" t="n">
         <v>22.29999923706055</v>
@@ -517,7 +517,7 @@
         <v>40329</v>
       </c>
       <c r="B3" t="n">
-        <v>7.019752025604248</v>
+        <v>7.019749164581299</v>
       </c>
       <c r="C3" t="n">
         <v>17.77000045776367</v>
@@ -536,7 +536,7 @@
         <v>40359</v>
       </c>
       <c r="B4" t="n">
-        <v>6.379795074462891</v>
+        <v>6.379794120788574</v>
       </c>
       <c r="C4" t="n">
         <v>16.14999961853027</v>
@@ -555,7 +555,7 @@
         <v>40390</v>
       </c>
       <c r="B5" t="n">
-        <v>7.110608100891113</v>
+        <v>7.110610008239746</v>
       </c>
       <c r="C5" t="n">
         <v>18</v>
@@ -593,7 +593,7 @@
         <v>40451</v>
       </c>
       <c r="B7" t="n">
-        <v>9.441303253173828</v>
+        <v>9.441307067871094</v>
       </c>
       <c r="C7" t="n">
         <v>23.89999961853027</v>
@@ -612,7 +612,7 @@
         <v>40482</v>
       </c>
       <c r="B8" t="n">
-        <v>10.61060428619385</v>
+        <v>10.6106071472168</v>
       </c>
       <c r="C8" t="n">
         <v>26.86000061035156</v>
@@ -631,7 +631,7 @@
         <v>40512</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53893852233887</v>
+        <v>11.53893280029297</v>
       </c>
       <c r="C9" t="n">
         <v>29.20999908447266</v>
@@ -669,7 +669,7 @@
         <v>40574</v>
       </c>
       <c r="B11" t="n">
-        <v>14.19751453399658</v>
+        <v>14.19751739501953</v>
       </c>
       <c r="C11" t="n">
         <v>35.93999862670898</v>
@@ -707,7 +707,7 @@
         <v>40633</v>
       </c>
       <c r="B13" t="n">
-        <v>15.62357997894287</v>
+        <v>15.62358665466309</v>
       </c>
       <c r="C13" t="n">
         <v>39.54999923706055</v>
@@ -726,7 +726,7 @@
         <v>40663</v>
       </c>
       <c r="B14" t="n">
-        <v>17.57900810241699</v>
+        <v>17.57900047302246</v>
       </c>
       <c r="C14" t="n">
         <v>44.5</v>
@@ -745,7 +745,7 @@
         <v>40694</v>
       </c>
       <c r="B15" t="n">
-        <v>17.34444808959961</v>
+        <v>17.34444999694824</v>
       </c>
       <c r="C15" t="n">
         <v>43.81000137329102</v>
@@ -764,7 +764,7 @@
         <v>40724</v>
       </c>
       <c r="B16" t="n">
-        <v>15.25013256072998</v>
+        <v>15.25012874603271</v>
       </c>
       <c r="C16" t="n">
         <v>38.52000045776367</v>
@@ -783,7 +783,7 @@
         <v>40755</v>
       </c>
       <c r="B17" t="n">
-        <v>15.62228107452393</v>
+        <v>15.62227535247803</v>
       </c>
       <c r="C17" t="n">
         <v>39.45999908447266</v>
@@ -821,7 +821,7 @@
         <v>40816</v>
       </c>
       <c r="B19" t="n">
-        <v>9.729277610778809</v>
+        <v>9.729281425476074</v>
       </c>
       <c r="C19" t="n">
         <v>24.43000030517578</v>
@@ -846,7 +846,7 @@
         <v>40847</v>
       </c>
       <c r="B20" t="n">
-        <v>13.08653163909912</v>
+        <v>13.08653259277344</v>
       </c>
       <c r="C20" t="n">
         <v>32.86000061035156</v>
@@ -871,7 +871,7 @@
         <v>40877</v>
       </c>
       <c r="B21" t="n">
-        <v>15.08752727508545</v>
+        <v>15.08753204345703</v>
       </c>
       <c r="C21" t="n">
         <v>32.66999816894531</v>
@@ -896,7 +896,7 @@
         <v>40908</v>
       </c>
       <c r="B22" t="n">
-        <v>15.00440502166748</v>
+        <v>15.00440406799316</v>
       </c>
       <c r="C22" t="n">
         <v>32.4900016784668</v>
@@ -921,7 +921,7 @@
         <v>40939</v>
       </c>
       <c r="B23" t="n">
-        <v>19.90427207946777</v>
+        <v>19.90427398681641</v>
       </c>
       <c r="C23" t="n">
         <v>43.09999847412109</v>
@@ -946,7 +946,7 @@
         <v>40968</v>
       </c>
       <c r="B24" t="n">
-        <v>19.94121360778809</v>
+        <v>19.94122123718262</v>
       </c>
       <c r="C24" t="n">
         <v>43.18000030517578</v>
@@ -971,7 +971,7 @@
         <v>40999</v>
       </c>
       <c r="B25" t="n">
-        <v>20.28316688537598</v>
+        <v>20.28317070007324</v>
       </c>
       <c r="C25" t="n">
         <v>43.65000152587891</v>
@@ -996,7 +996,7 @@
         <v>41029</v>
       </c>
       <c r="B26" t="n">
-        <v>19.41422653198242</v>
+        <v>19.41422271728516</v>
       </c>
       <c r="C26" t="n">
         <v>41.77999877929688</v>
@@ -1021,7 +1021,7 @@
         <v>41060</v>
       </c>
       <c r="B27" t="n">
-        <v>18.52510261535645</v>
+        <v>18.52510643005371</v>
       </c>
       <c r="C27" t="n">
         <v>39.45999908447266</v>
@@ -1046,7 +1046,7 @@
         <v>41090</v>
       </c>
       <c r="B28" t="n">
-        <v>18.90537643432617</v>
+        <v>18.90537452697754</v>
       </c>
       <c r="C28" t="n">
         <v>40.27000045776367</v>
@@ -1071,7 +1071,7 @@
         <v>41121</v>
       </c>
       <c r="B29" t="n">
-        <v>20.9052906036377</v>
+        <v>20.90529632568359</v>
       </c>
       <c r="C29" t="n">
         <v>44.52999877929688</v>
@@ -1096,7 +1096,7 @@
         <v>41152</v>
       </c>
       <c r="B30" t="n">
-        <v>23.1242847442627</v>
+        <v>23.12429428100586</v>
       </c>
       <c r="C30" t="n">
         <v>48.84000015258789</v>
@@ -1121,7 +1121,7 @@
         <v>41182</v>
       </c>
       <c r="B31" t="n">
-        <v>24.4594898223877</v>
+        <v>24.45947647094727</v>
       </c>
       <c r="C31" t="n">
         <v>51.65999984741211</v>
@@ -1146,7 +1146,7 @@
         <v>41213</v>
       </c>
       <c r="B32" t="n">
-        <v>25.27858352661133</v>
+        <v>25.27857208251953</v>
       </c>
       <c r="C32" t="n">
         <v>53.38999938964844</v>
@@ -1171,7 +1171,7 @@
         <v>41243</v>
       </c>
       <c r="B33" t="n">
-        <v>25.15594291687012</v>
+        <v>25.15594673156738</v>
       </c>
       <c r="C33" t="n">
         <v>49.72999954223633</v>
@@ -1196,7 +1196,7 @@
         <v>41274</v>
       </c>
       <c r="B34" t="n">
-        <v>28.87900352478027</v>
+        <v>28.87900543212891</v>
       </c>
       <c r="C34" t="n">
         <v>57.09000015258789</v>
@@ -1246,7 +1246,7 @@
         <v>41333</v>
       </c>
       <c r="B36" t="n">
-        <v>29.85110092163086</v>
+        <v>29.85111427307129</v>
       </c>
       <c r="C36" t="n">
         <v>58.61999893188477</v>
@@ -1275,7 +1275,7 @@
         <v>41364</v>
       </c>
       <c r="B37" t="n">
-        <v>32.22921371459961</v>
+        <v>32.22920989990234</v>
       </c>
       <c r="C37" t="n">
         <v>63.29000091552734</v>
@@ -1304,7 +1304,7 @@
         <v>41394</v>
       </c>
       <c r="B38" t="n">
-        <v>30.91031265258789</v>
+        <v>30.91030883789062</v>
       </c>
       <c r="C38" t="n">
         <v>60.70000076293945</v>
@@ -1333,7 +1333,7 @@
         <v>41425</v>
       </c>
       <c r="B39" t="n">
-        <v>34.19821548461914</v>
+        <v>34.19821166992188</v>
       </c>
       <c r="C39" t="n">
         <v>66.65000152587891</v>
@@ -1362,7 +1362,7 @@
         <v>41455</v>
       </c>
       <c r="B40" t="n">
-        <v>33.99810409545898</v>
+        <v>33.99810028076172</v>
       </c>
       <c r="C40" t="n">
         <v>66.26000213623047</v>
@@ -1420,7 +1420,7 @@
         <v>41517</v>
       </c>
       <c r="B42" t="n">
-        <v>35.99407958984375</v>
+        <v>35.99407196044922</v>
       </c>
       <c r="C42" t="n">
         <v>70.15000152587891</v>
@@ -1478,7 +1478,7 @@
         <v>41578</v>
       </c>
       <c r="B44" t="n">
-        <v>38.53999710083008</v>
+        <v>38.54001235961914</v>
       </c>
       <c r="C44" t="n">
         <v>74.59999847412109</v>
@@ -1507,7 +1507,7 @@
         <v>41608</v>
       </c>
       <c r="B45" t="n">
-        <v>40.18395233154297</v>
+        <v>40.18395614624023</v>
       </c>
       <c r="C45" t="n">
         <v>77.18000030517578</v>
@@ -1536,7 +1536,7 @@
         <v>41639</v>
       </c>
       <c r="B46" t="n">
-        <v>41.7979850769043</v>
+        <v>41.79796600341797</v>
       </c>
       <c r="C46" t="n">
         <v>80.27999877929688</v>
@@ -1565,7 +1565,7 @@
         <v>41670</v>
       </c>
       <c r="B47" t="n">
-        <v>41.00659942626953</v>
+        <v>41.00659561157227</v>
       </c>
       <c r="C47" t="n">
         <v>78.76000213623047</v>
@@ -1594,7 +1594,7 @@
         <v>41698</v>
       </c>
       <c r="B48" t="n">
-        <v>46.17599868774414</v>
+        <v>46.17599105834961</v>
       </c>
       <c r="C48" t="n">
         <v>88.08000183105469</v>
@@ -1623,7 +1623,7 @@
         <v>41729</v>
       </c>
       <c r="B49" t="n">
-        <v>46.6268424987793</v>
+        <v>46.62685012817383</v>
       </c>
       <c r="C49" t="n">
         <v>88.94000244140625</v>
@@ -1681,7 +1681,7 @@
         <v>41790</v>
       </c>
       <c r="B51" t="n">
-        <v>52.59853744506836</v>
+        <v>52.59854125976562</v>
       </c>
       <c r="C51" t="n">
         <v>99.56999969482422</v>
@@ -1710,7 +1710,7 @@
         <v>41820</v>
       </c>
       <c r="B52" t="n">
-        <v>51.58426666259766</v>
+        <v>51.58429718017578</v>
       </c>
       <c r="C52" t="n">
         <v>97.65000152587891</v>
@@ -1739,7 +1739,7 @@
         <v>41851</v>
       </c>
       <c r="B53" t="n">
-        <v>56.12730407714844</v>
+        <v>56.12730026245117</v>
       </c>
       <c r="C53" t="n">
         <v>106.25</v>
@@ -1768,7 +1768,7 @@
         <v>41882</v>
       </c>
       <c r="B54" t="n">
-        <v>60.78549957275391</v>
+        <v>60.78550338745117</v>
       </c>
       <c r="C54" t="n">
         <v>114.3499984741211</v>
@@ -1826,7 +1826,7 @@
         <v>41943</v>
       </c>
       <c r="B56" t="n">
-        <v>48.7081298828125</v>
+        <v>48.7081413269043</v>
       </c>
       <c r="C56" t="n">
         <v>91.62999725341797</v>
@@ -1855,7 +1855,7 @@
         <v>41973</v>
       </c>
       <c r="B57" t="n">
-        <v>42.25094985961914</v>
+        <v>42.25094223022461</v>
       </c>
       <c r="C57" t="n">
         <v>78.86000061035156</v>
@@ -1884,7 +1884,7 @@
         <v>42004</v>
       </c>
       <c r="B58" t="n">
-        <v>42.53490829467773</v>
+        <v>42.53491592407227</v>
       </c>
       <c r="C58" t="n">
         <v>79.38999938964844</v>
@@ -1913,7 +1913,7 @@
         <v>42035</v>
       </c>
       <c r="B59" t="n">
-        <v>42.37416839599609</v>
+        <v>42.37417602539062</v>
       </c>
       <c r="C59" t="n">
         <v>79.08999633789062</v>
@@ -1971,7 +1971,7 @@
         <v>42094</v>
       </c>
       <c r="B61" t="n">
-        <v>47.41119003295898</v>
+        <v>47.41120529174805</v>
       </c>
       <c r="C61" t="n">
         <v>87.80000305175781</v>
@@ -2029,7 +2029,7 @@
         <v>42155</v>
       </c>
       <c r="B63" t="n">
-        <v>54.59304809570312</v>
+        <v>54.59307861328125</v>
       </c>
       <c r="C63" t="n">
         <v>101.0999984741211</v>
@@ -2116,7 +2116,7 @@
         <v>42247</v>
       </c>
       <c r="B66" t="n">
-        <v>46.53701782226562</v>
+        <v>46.53701400756836</v>
       </c>
       <c r="C66" t="n">
         <v>85.37999725341797</v>
@@ -2145,7 +2145,7 @@
         <v>42277</v>
       </c>
       <c r="B67" t="n">
-        <v>45.43598937988281</v>
+        <v>45.43598175048828</v>
       </c>
       <c r="C67" t="n">
         <v>83.36000061035156</v>
@@ -2174,7 +2174,7 @@
         <v>42308</v>
       </c>
       <c r="B68" t="n">
-        <v>50.64129638671875</v>
+        <v>50.64128875732422</v>
       </c>
       <c r="C68" t="n">
         <v>92.91000366210938</v>
@@ -2203,7 +2203,7 @@
         <v>42338</v>
       </c>
       <c r="B69" t="n">
-        <v>52.65944671630859</v>
+        <v>52.65943145751953</v>
       </c>
       <c r="C69" t="n">
         <v>95.81999969482422</v>
@@ -2232,7 +2232,7 @@
         <v>42369</v>
       </c>
       <c r="B70" t="n">
-        <v>47.75732040405273</v>
+        <v>47.75732421875</v>
       </c>
       <c r="C70" t="n">
         <v>86.90000152587891</v>
@@ -2261,7 +2261,7 @@
         <v>42400</v>
       </c>
       <c r="B71" t="n">
-        <v>42.84969329833984</v>
+        <v>42.84968566894531</v>
       </c>
       <c r="C71" t="n">
         <v>77.97000122070312</v>
@@ -2290,7 +2290,7 @@
         <v>42429</v>
       </c>
       <c r="B72" t="n">
-        <v>44.52452850341797</v>
+        <v>44.52454376220703</v>
       </c>
       <c r="C72" t="n">
         <v>80.20999908447266</v>
@@ -2319,7 +2319,7 @@
         <v>42460</v>
       </c>
       <c r="B73" t="n">
-        <v>47.50541687011719</v>
+        <v>47.50542831420898</v>
       </c>
       <c r="C73" t="n">
         <v>85.58000183105469</v>
@@ -2348,7 +2348,7 @@
         <v>42490</v>
       </c>
       <c r="B74" t="n">
-        <v>45.89009857177734</v>
+        <v>45.89009094238281</v>
       </c>
       <c r="C74" t="n">
         <v>82.66999816894531</v>
@@ -2406,7 +2406,7 @@
         <v>42551</v>
       </c>
       <c r="B76" t="n">
-        <v>41.74955749511719</v>
+        <v>41.74954605102539</v>
       </c>
       <c r="C76" t="n">
         <v>74.41999816894531</v>
@@ -2464,7 +2464,7 @@
         <v>42613</v>
       </c>
       <c r="B78" t="n">
-        <v>44.75362396240234</v>
+        <v>44.75362014770508</v>
       </c>
       <c r="C78" t="n">
         <v>78.88999938964844</v>
@@ -2522,7 +2522,7 @@
         <v>42674</v>
       </c>
       <c r="B80" t="n">
-        <v>45.12804794311523</v>
+        <v>45.1280403137207</v>
       </c>
       <c r="C80" t="n">
         <v>79.55000305175781</v>
@@ -2551,7 +2551,7 @@
         <v>42704</v>
       </c>
       <c r="B81" t="n">
-        <v>51.74543762207031</v>
+        <v>51.74542999267578</v>
       </c>
       <c r="C81" t="n">
         <v>90.31999969482422</v>
@@ -2580,7 +2580,7 @@
         <v>42735</v>
       </c>
       <c r="B82" t="n">
-        <v>49.1443977355957</v>
+        <v>49.14441299438477</v>
       </c>
       <c r="C82" t="n">
         <v>85.77999877929688</v>
@@ -2609,7 +2609,7 @@
         <v>42766</v>
       </c>
       <c r="B83" t="n">
-        <v>53.43552398681641</v>
+        <v>53.4355354309082</v>
       </c>
       <c r="C83" t="n">
         <v>93.26999664306641</v>
@@ -2638,7 +2638,7 @@
         <v>42794</v>
       </c>
       <c r="B84" t="n">
-        <v>52.27249145507812</v>
+        <v>52.27249908447266</v>
       </c>
       <c r="C84" t="n">
         <v>91.23999786376953</v>
@@ -2667,7 +2667,7 @@
         <v>42825</v>
       </c>
       <c r="B85" t="n">
-        <v>52.72116851806641</v>
+        <v>52.72114562988281</v>
       </c>
       <c r="C85" t="n">
         <v>91.19000244140625</v>
@@ -2696,7 +2696,7 @@
         <v>42855</v>
       </c>
       <c r="B86" t="n">
-        <v>49.00368499755859</v>
+        <v>49.00367736816406</v>
       </c>
       <c r="C86" t="n">
         <v>84.76000213623047</v>
@@ -2725,7 +2725,7 @@
         <v>42886</v>
       </c>
       <c r="B87" t="n">
-        <v>46.55233001708984</v>
+        <v>46.55233383178711</v>
       </c>
       <c r="C87" t="n">
         <v>80.51999664306641</v>
@@ -2754,7 +2754,7 @@
         <v>42916</v>
       </c>
       <c r="B88" t="n">
-        <v>49.34128189086914</v>
+        <v>49.34126663208008</v>
       </c>
       <c r="C88" t="n">
         <v>84.38999938964844</v>
@@ -2783,7 +2783,7 @@
         <v>42947</v>
       </c>
       <c r="B89" t="n">
-        <v>52.6739616394043</v>
+        <v>52.67395782470703</v>
       </c>
       <c r="C89" t="n">
         <v>90.08999633789062</v>
@@ -2812,7 +2812,7 @@
         <v>42978</v>
       </c>
       <c r="B90" t="n">
-        <v>52.96628952026367</v>
+        <v>52.9662971496582</v>
       </c>
       <c r="C90" t="n">
         <v>90.58999633789062</v>
@@ -2841,7 +2841,7 @@
         <v>43008</v>
       </c>
       <c r="B91" t="n">
-        <v>58.49383163452148</v>
+        <v>58.49381637573242</v>
       </c>
       <c r="C91" t="n">
         <v>99.05000305175781</v>
@@ -2870,7 +2870,7 @@
         <v>43039</v>
       </c>
       <c r="B92" t="n">
-        <v>61.13949203491211</v>
+        <v>61.13948822021484</v>
       </c>
       <c r="C92" t="n">
         <v>103.5299987792969</v>
@@ -2899,7 +2899,7 @@
         <v>43069</v>
       </c>
       <c r="B93" t="n">
-        <v>61.83041763305664</v>
+        <v>61.83041000366211</v>
       </c>
       <c r="C93" t="n">
         <v>104.6999969482422</v>
@@ -2928,7 +2928,7 @@
         <v>43100</v>
       </c>
       <c r="B94" t="n">
-        <v>65.71746063232422</v>
+        <v>65.71747589111328</v>
       </c>
       <c r="C94" t="n">
         <v>110.3199996948242</v>
@@ -2957,7 +2957,7 @@
         <v>43131</v>
       </c>
       <c r="B95" t="n">
-        <v>71.38850402832031</v>
+        <v>71.38851928710938</v>
       </c>
       <c r="C95" t="n">
         <v>119.8399963378906</v>
@@ -2986,7 +2986,7 @@
         <v>43159</v>
       </c>
       <c r="B96" t="n">
-        <v>64.46651458740234</v>
+        <v>64.46649932861328</v>
       </c>
       <c r="C96" t="n">
         <v>108.2200012207031</v>
@@ -3044,7 +3044,7 @@
         <v>43220</v>
       </c>
       <c r="B98" t="n">
-        <v>63.57112884521484</v>
+        <v>63.57113265991211</v>
       </c>
       <c r="C98" t="n">
         <v>105.7300033569336</v>
@@ -3073,7 +3073,7 @@
         <v>43251</v>
       </c>
       <c r="B99" t="n">
-        <v>67.41316986083984</v>
+        <v>67.41317749023438</v>
       </c>
       <c r="C99" t="n">
         <v>112.120002746582</v>
@@ -3102,7 +3102,7 @@
         <v>43281</v>
       </c>
       <c r="B100" t="n">
-        <v>66.61024475097656</v>
+        <v>66.61023712158203</v>
       </c>
       <c r="C100" t="n">
         <v>109.8499984741211</v>
@@ -3131,7 +3131,7 @@
         <v>43312</v>
       </c>
       <c r="B101" t="n">
-        <v>67.18022918701172</v>
+        <v>67.18024444580078</v>
       </c>
       <c r="C101" t="n">
         <v>110.7900009155273</v>
@@ -3160,7 +3160,7 @@
         <v>43343</v>
       </c>
       <c r="B102" t="n">
-        <v>68.38691711425781</v>
+        <v>68.38690185546875</v>
       </c>
       <c r="C102" t="n">
         <v>112.7799987792969</v>
@@ -3189,7 +3189,7 @@
         <v>43373</v>
       </c>
       <c r="B103" t="n">
-        <v>62.71554946899414</v>
+        <v>62.71553421020508</v>
       </c>
       <c r="C103" t="n">
         <v>102.5100021362305</v>
@@ -3218,7 +3218,7 @@
         <v>43404</v>
       </c>
       <c r="B104" t="n">
-        <v>54.61531448364258</v>
+        <v>54.61531066894531</v>
       </c>
       <c r="C104" t="n">
         <v>89.26999664306641</v>
@@ -3247,7 +3247,7 @@
         <v>43434</v>
       </c>
       <c r="B105" t="n">
-        <v>57.08698654174805</v>
+        <v>57.08698272705078</v>
       </c>
       <c r="C105" t="n">
         <v>93.30999755859375</v>
@@ -3276,7 +3276,7 @@
         <v>43465</v>
       </c>
       <c r="B106" t="n">
-        <v>51.46047973632812</v>
+        <v>51.46047210693359</v>
       </c>
       <c r="C106" t="n">
         <v>83.16000366210938</v>
@@ -3305,7 +3305,7 @@
         <v>43496</v>
       </c>
       <c r="B107" t="n">
-        <v>53.81815338134766</v>
+        <v>53.81815719604492</v>
       </c>
       <c r="C107" t="n">
         <v>86.97000122070312</v>
@@ -3334,7 +3334,7 @@
         <v>43524</v>
       </c>
       <c r="B108" t="n">
-        <v>52.92086410522461</v>
+        <v>52.92089080810547</v>
       </c>
       <c r="C108" t="n">
         <v>85.51999664306641</v>
@@ -3363,7 +3363,7 @@
         <v>43555</v>
       </c>
       <c r="B109" t="n">
-        <v>52.64538192749023</v>
+        <v>52.6453857421875</v>
       </c>
       <c r="C109" t="n">
         <v>84.08000183105469</v>
@@ -3392,7 +3392,7 @@
         <v>43585</v>
       </c>
       <c r="B110" t="n">
-        <v>55.24382781982422</v>
+        <v>55.24384689331055</v>
       </c>
       <c r="C110" t="n">
         <v>88.23000335693359</v>
@@ -3421,7 +3421,7 @@
         <v>43616</v>
       </c>
       <c r="B111" t="n">
-        <v>46.49047470092773</v>
+        <v>46.49048614501953</v>
       </c>
       <c r="C111" t="n">
         <v>74.25</v>
@@ -3450,7 +3450,7 @@
         <v>43646</v>
       </c>
       <c r="B112" t="n">
-        <v>54.64292526245117</v>
+        <v>54.64292144775391</v>
       </c>
       <c r="C112" t="n">
         <v>86.12999725341797</v>
@@ -3479,7 +3479,7 @@
         <v>43677</v>
       </c>
       <c r="B113" t="n">
-        <v>53.09493637084961</v>
+        <v>53.09493255615234</v>
       </c>
       <c r="C113" t="n">
         <v>83.69000244140625</v>
@@ -3508,7 +3508,7 @@
         <v>43708</v>
       </c>
       <c r="B114" t="n">
-        <v>49.09171295166016</v>
+        <v>49.09171676635742</v>
       </c>
       <c r="C114" t="n">
         <v>77.37999725341797</v>
@@ -3537,7 +3537,7 @@
         <v>43738</v>
       </c>
       <c r="B115" t="n">
-        <v>57.54271697998047</v>
+        <v>57.54270553588867</v>
       </c>
       <c r="C115" t="n">
         <v>89.47000122070312</v>
@@ -3566,7 +3566,7 @@
         <v>43769</v>
       </c>
       <c r="B116" t="n">
-        <v>57.69064712524414</v>
+        <v>57.6906623840332</v>
       </c>
       <c r="C116" t="n">
         <v>89.69999694824219</v>
@@ -3595,7 +3595,7 @@
         <v>43799</v>
       </c>
       <c r="B117" t="n">
-        <v>60.18558502197266</v>
+        <v>60.18556213378906</v>
       </c>
       <c r="C117" t="n">
         <v>92.54000091552734</v>
@@ -3624,7 +3624,7 @@
         <v>43830</v>
       </c>
       <c r="B118" t="n">
-        <v>61.44728469848633</v>
+        <v>61.44729232788086</v>
       </c>
       <c r="C118" t="n">
         <v>94.48000335693359</v>
@@ -3653,7 +3653,7 @@
         <v>43861</v>
       </c>
       <c r="B119" t="n">
-        <v>50.63809204101562</v>
+        <v>50.6380729675293</v>
       </c>
       <c r="C119" t="n">
         <v>77.86000061035156</v>
@@ -3682,7 +3682,7 @@
         <v>43890</v>
       </c>
       <c r="B120" t="n">
-        <v>47.17432022094727</v>
+        <v>47.17433166503906</v>
       </c>
       <c r="C120" t="n">
         <v>71.45999908447266</v>
@@ -3711,7 +3711,7 @@
         <v>43921</v>
       </c>
       <c r="B121" t="n">
-        <v>32.76325988769531</v>
+        <v>32.76325607299805</v>
       </c>
       <c r="C121" t="n">
         <v>49.63000106811523</v>
@@ -3740,7 +3740,7 @@
         <v>43951</v>
       </c>
       <c r="B122" t="n">
-        <v>38.25569534301758</v>
+        <v>38.25569915771484</v>
       </c>
       <c r="C122" t="n">
         <v>57.95000076293945</v>
@@ -3769,7 +3769,7 @@
         <v>43982</v>
       </c>
       <c r="B123" t="n">
-        <v>42.09117126464844</v>
+        <v>42.09117889404297</v>
       </c>
       <c r="C123" t="n">
         <v>63.7599983215332</v>
@@ -3827,7 +3827,7 @@
         <v>44043</v>
       </c>
       <c r="B125" t="n">
-        <v>41.86704635620117</v>
+        <v>41.86704254150391</v>
       </c>
       <c r="C125" t="n">
         <v>62.52000045776367</v>
@@ -3856,7 +3856,7 @@
         <v>44074</v>
       </c>
       <c r="B126" t="n">
-        <v>44.52761459350586</v>
+        <v>44.52761077880859</v>
       </c>
       <c r="C126" t="n">
         <v>65.48000335693359</v>
@@ -3914,7 +3914,7 @@
         <v>44135</v>
       </c>
       <c r="B128" t="n">
-        <v>46.54727554321289</v>
+        <v>46.54727935791016</v>
       </c>
       <c r="C128" t="n">
         <v>68.44999694824219</v>
@@ -3943,7 +3943,7 @@
         <v>44165</v>
       </c>
       <c r="B129" t="n">
-        <v>58.5578727722168</v>
+        <v>58.55787658691406</v>
       </c>
       <c r="C129" t="n">
         <v>85.09999847412109</v>
@@ -3972,7 +3972,7 @@
         <v>44196</v>
       </c>
       <c r="B130" t="n">
-        <v>63.07186126708984</v>
+        <v>63.07185745239258</v>
       </c>
       <c r="C130" t="n">
         <v>91.66000366210938</v>
@@ -4001,7 +4001,7 @@
         <v>44227</v>
       </c>
       <c r="B131" t="n">
-        <v>59.01203918457031</v>
+        <v>59.01205444335938</v>
       </c>
       <c r="C131" t="n">
         <v>85.76000213623047</v>
@@ -4059,7 +4059,7 @@
         <v>44286</v>
       </c>
       <c r="B133" t="n">
-        <v>72.31266021728516</v>
+        <v>72.31267547607422</v>
       </c>
       <c r="C133" t="n">
         <v>104.0500030517578</v>
@@ -4088,7 +4088,7 @@
         <v>44316</v>
       </c>
       <c r="B134" t="n">
-        <v>72.09721374511719</v>
+        <v>72.09722137451172</v>
       </c>
       <c r="C134" t="n">
         <v>103.7399978637695</v>
@@ -4117,7 +4117,7 @@
         <v>44347</v>
       </c>
       <c r="B135" t="n">
-        <v>78.26863861083984</v>
+        <v>78.26862335205078</v>
       </c>
       <c r="C135" t="n">
         <v>112.620002746582</v>
@@ -4146,7 +4146,7 @@
         <v>44377</v>
       </c>
       <c r="B136" t="n">
-        <v>72.18466186523438</v>
+        <v>72.18466949462891</v>
       </c>
       <c r="C136" t="n">
         <v>102.870002746582</v>
@@ -4175,7 +4175,7 @@
         <v>44408</v>
       </c>
       <c r="B137" t="n">
-        <v>69.70063018798828</v>
+        <v>69.70062255859375</v>
       </c>
       <c r="C137" t="n">
         <v>99.33000183105469</v>
@@ -4204,7 +4204,7 @@
         <v>44439</v>
       </c>
       <c r="B138" t="n">
-        <v>71.21158599853516</v>
+        <v>71.21157836914062</v>
       </c>
       <c r="C138" t="n">
         <v>100.3499984741211</v>
@@ -4233,7 +4233,7 @@
         <v>44469</v>
       </c>
       <c r="B139" t="n">
-        <v>66.59897613525391</v>
+        <v>66.59898376464844</v>
       </c>
       <c r="C139" t="n">
         <v>93.84999847412109</v>
@@ -4262,7 +4262,7 @@
         <v>44500</v>
       </c>
       <c r="B140" t="n">
-        <v>65.86805725097656</v>
+        <v>65.86806488037109</v>
       </c>
       <c r="C140" t="n">
         <v>92.81999969482422</v>
@@ -4291,7 +4291,7 @@
         <v>44530</v>
       </c>
       <c r="B141" t="n">
-        <v>62.60286331176758</v>
+        <v>62.60287475585938</v>
       </c>
       <c r="C141" t="n">
         <v>87.12999725341797</v>
@@ -4320,7 +4320,7 @@
         <v>44561</v>
       </c>
       <c r="B142" t="n">
-        <v>66.2672119140625</v>
+        <v>66.26721954345703</v>
       </c>
       <c r="C142" t="n">
         <v>92.23000335693359</v>
@@ -4378,7 +4378,7 @@
         <v>44620</v>
       </c>
       <c r="B144" t="n">
-        <v>69.85971832275391</v>
+        <v>69.85972595214844</v>
       </c>
       <c r="C144" t="n">
         <v>97.23000335693359</v>
@@ -4407,7 +4407,7 @@
         <v>44651</v>
       </c>
       <c r="B145" t="n">
-        <v>74.72201538085938</v>
+        <v>74.72200775146484</v>
       </c>
       <c r="C145" t="n">
         <v>102.8199996948242</v>
@@ -4436,7 +4436,7 @@
         <v>44681</v>
       </c>
       <c r="B146" t="n">
-        <v>77.05480194091797</v>
+        <v>77.05479431152344</v>
       </c>
       <c r="C146" t="n">
         <v>106.0299987792969</v>
@@ -4465,7 +4465,7 @@
         <v>44712</v>
       </c>
       <c r="B147" t="n">
-        <v>83.02849578857422</v>
+        <v>83.02848052978516</v>
       </c>
       <c r="C147" t="n">
         <v>114.25</v>
@@ -4523,7 +4523,7 @@
         <v>44773</v>
       </c>
       <c r="B149" t="n">
-        <v>68.56756591796875</v>
+        <v>68.56757354736328</v>
       </c>
       <c r="C149" t="n">
         <v>89.12000274658203</v>
@@ -4552,7 +4552,7 @@
         <v>44804</v>
       </c>
       <c r="B150" t="n">
-        <v>64.70771026611328</v>
+        <v>64.70772552490234</v>
       </c>
       <c r="C150" t="n">
         <v>83</v>
@@ -4610,7 +4610,7 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>59.60126113891602</v>
+        <v>59.60126876831055</v>
       </c>
       <c r="C152" t="n">
         <v>76.44999694824219</v>
@@ -4639,7 +4639,7 @@
         <v>44895</v>
       </c>
       <c r="B153" t="n">
-        <v>67.18231201171875</v>
+        <v>67.18230438232422</v>
       </c>
       <c r="C153" t="n">
         <v>85.01000213623047</v>
@@ -4668,7 +4668,7 @@
         <v>44926</v>
       </c>
       <c r="B154" t="n">
-        <v>65.61753082275391</v>
+        <v>65.61753845214844</v>
       </c>
       <c r="C154" t="n">
         <v>83.02999877929688</v>
@@ -4697,7 +4697,7 @@
         <v>44957</v>
       </c>
       <c r="B155" t="n">
-        <v>76.41285705566406</v>
+        <v>76.41286468505859</v>
       </c>
       <c r="C155" t="n">
         <v>96.69000244140625</v>
@@ -4726,7 +4726,7 @@
         <v>44985</v>
       </c>
       <c r="B156" t="n">
-        <v>75.85964202880859</v>
+        <v>75.85965728759766</v>
       </c>
       <c r="C156" t="n">
         <v>95.98999786376953</v>
@@ -4755,7 +4755,7 @@
         <v>45016</v>
       </c>
       <c r="B157" t="n">
-        <v>75.11504364013672</v>
+        <v>75.11505126953125</v>
       </c>
       <c r="C157" t="n">
         <v>93.88999938964844</v>
@@ -4784,7 +4784,7 @@
         <v>45046</v>
       </c>
       <c r="B158" t="n">
-        <v>75.69108581542969</v>
+        <v>75.69109344482422</v>
       </c>
       <c r="C158" t="n">
         <v>94.61000061035156</v>
@@ -4842,7 +4842,7 @@
         <v>45107</v>
       </c>
       <c r="B160" t="n">
-        <v>74.51628875732422</v>
+        <v>74.51626586914062</v>
       </c>
       <c r="C160" t="n">
         <v>91.83000183105469</v>
@@ -4871,7 +4871,7 @@
         <v>45138</v>
       </c>
       <c r="B161" t="n">
-        <v>80.22083282470703</v>
+        <v>80.22084045410156</v>
       </c>
       <c r="C161" t="n">
         <v>98.86000061035156</v>
@@ -4987,7 +4987,7 @@
         <v>45260</v>
       </c>
       <c r="B165" t="n">
-        <v>79.21700286865234</v>
+        <v>79.21701049804688</v>
       </c>
       <c r="C165" t="n">
         <v>95.09999847412109</v>
@@ -5016,7 +5016,7 @@
         <v>45291</v>
       </c>
       <c r="B166" t="n">
-        <v>79.20036315917969</v>
+        <v>79.20034790039062</v>
       </c>
       <c r="C166" t="n">
         <v>95.08000183105469</v>
@@ -5045,7 +5045,7 @@
         <v>45322</v>
       </c>
       <c r="B167" t="n">
-        <v>78.40069580078125</v>
+        <v>78.40070343017578</v>
       </c>
       <c r="C167" t="n">
         <v>94.12000274658203</v>
@@ -5074,7 +5074,7 @@
         <v>45351</v>
       </c>
       <c r="B168" t="n">
-        <v>83.53187561035156</v>
+        <v>83.53188323974609</v>
       </c>
       <c r="C168" t="n">
         <v>100.2799987792969</v>
@@ -5161,7 +5161,7 @@
         <v>45443</v>
       </c>
       <c r="B171" t="n">
-        <v>83.86084747314453</v>
+        <v>83.86085510253906</v>
       </c>
       <c r="C171" t="n">
         <v>99.41999816894531</v>
@@ -5190,7 +5190,7 @@
         <v>45473</v>
       </c>
       <c r="B172" t="n">
-        <v>81.79170227050781</v>
+        <v>81.79170989990234</v>
       </c>
       <c r="C172" t="n">
         <v>95.66000366210938</v>
@@ -5248,7 +5248,7 @@
         <v>45535</v>
       </c>
       <c r="B174" t="n">
-        <v>85.55738830566406</v>
+        <v>85.55738067626953</v>
       </c>
       <c r="C174" t="n">
         <v>98.69999694824219</v>
@@ -5364,7 +5364,7 @@
         <v>45657</v>
       </c>
       <c r="B178" t="n">
-        <v>65.4324951171875</v>
+        <v>65.43248748779297</v>
       </c>
       <c r="C178" t="n">
         <v>74.26999664306641</v>
@@ -5422,7 +5422,7 @@
         <v>45716</v>
       </c>
       <c r="B180" t="n">
-        <v>67.68787384033203</v>
+        <v>67.6878662109375</v>
       </c>
       <c r="C180" t="n">
         <v>76.83000183105469</v>
@@ -5480,7 +5480,7 @@
         <v>45777</v>
       </c>
       <c r="B182" t="n">
-        <v>52.18579864501953</v>
+        <v>52.1858024597168</v>
       </c>
       <c r="C182" t="n">
         <v>58.20999908447266</v>
@@ -5509,7 +5509,7 @@
         <v>45808</v>
       </c>
       <c r="B183" t="n">
-        <v>50.64380645751953</v>
+        <v>50.6438102722168</v>
       </c>
       <c r="C183" t="n">
         <v>56.4900016784668</v>
@@ -5567,7 +5567,7 @@
         <v>45869</v>
       </c>
       <c r="B185" t="n">
-        <v>53.22560882568359</v>
+        <v>53.22560501098633</v>
       </c>
       <c r="C185" t="n">
         <v>57.93000030517578</v>
@@ -5625,7 +5625,7 @@
         <v>45930</v>
       </c>
       <c r="B187" t="n">
-        <v>46.13296890258789</v>
+        <v>46.13296127319336</v>
       </c>
       <c r="C187" t="n">
         <v>49.04000091552734</v>
@@ -5681,7 +5681,7 @@
         <v>45991</v>
       </c>
       <c r="B189" t="n">
-        <v>46.08592987060547</v>
+        <v>46.08593368530273</v>
       </c>
       <c r="C189" t="n">
         <v>48.9900016784668</v>
@@ -5762,7 +5762,7 @@
         <v>46081</v>
       </c>
       <c r="B192" t="n">
-        <v>55.6670036315918</v>
+        <v>55.66699981689453</v>
       </c>
       <c r="C192" t="n">
         <v>57.52000045776367</v>
